--- a/data/srleng/P3/P3T1_Reading WS2 (End Rhymes).xlsx
+++ b/data/srleng/P3/P3T1_Reading WS2 (End Rhymes).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Github/word-review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E8567-B1DE-4F4F-8A32-BBFEF1DFFA2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9181EF16-873B-9D47-9BEC-01D0294A1214}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
   <si>
     <t>phonetics</t>
   </si>
@@ -424,6 +424,21 @@
   <si>
     <t>沒有句子</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foam</t>
+  </si>
+  <si>
+    <t>泡沫</t>
+  </si>
+  <si>
+    <t>/fəʊm/</t>
+  </si>
+  <si>
+    <t>A mass of small bubbles on the surface of liquid</t>
+  </si>
+  <si>
+    <t>The dark part of each day when the sun is down</t>
   </si>
 </sst>
 </file>
@@ -802,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -1018,422 +1033,482 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C19">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="C21">
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C23">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C24">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C25">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C27">
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C29">
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
         <v>96</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E33" t="s">
         <v>94</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F33" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
